--- a/data/extra2/Q&A_medium.xlsx
+++ b/data/extra2/Q&A_medium.xlsx
@@ -694,7 +694,7 @@
   FROM dws_cust_fin_d
   WHERE data_dt BETWEEN '20260101' AND '20260331'
   GROUP BY pty_id
-  HAVING SUM(coalesce(assign_in, 0)) &gt; 0
+  HAVING SUM(coalesce(tran_in, 0)) &gt; 0
 ) AS t</t>
         </is>
       </c>
